--- a/data/rule_library/goose.xlsx
+++ b/data/rule_library/goose.xlsx
@@ -346,6 +346,34 @@
       <rPr>
         <sz val="9"/>
         <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家，显示其本回合是否有杀戮行为，有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同一玩家每回合仅可查</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -358,7 +386,37 @@
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t>名玩家，显示其本回合是否有杀戮行为，同一玩家仅可查</t>
+      <t>次。</t>
+    </r>
+  </si>
+  <si>
+    <t>精准锁定作案嫌疑人，为阵营提供关键线索，需及时分享查询结果。</t>
+  </si>
+  <si>
+    <t>开局查询动线异常或单独行动的玩家，快速排除嫌疑；中期优先查询报警人、尸体发现者，验证其身份；后期每轮查询后立即公开结果，带领团队锁定凶手，避免信息滞后。</t>
+  </si>
+  <si>
+    <t>首轮可查抱团核心玩家，快速确认队友；若查到有杀戮行为的玩家，先私下与信息位核对，再公开指控。</t>
+  </si>
+  <si>
+    <t>通灵者</t>
+  </si>
+  <si>
+    <t>使用技能可查看场上存活幽灵的数量。有CD</t>
+  </si>
+  <si>
+    <t>辅助型信息位，通过幽灵数变化判断是否有隐刀，帮助团队梳理局势。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>开局每</t>
     </r>
     <r>
       <rPr>
@@ -367,35 +425,77 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次。</t>
-    </r>
-  </si>
-  <si>
-    <t>精准锁定作案嫌疑人，为阵营提供关键线索，需及时分享查询结果。</t>
-  </si>
-  <si>
-    <t>开局查询动线异常或单独行动的玩家，快速排除嫌疑；中期优先查询报警人、尸体发现者，验证其身份；后期每轮查询后立即公开结果，带领团队锁定凶手，避免信息滞后。</t>
-  </si>
-  <si>
-    <t>首轮可查抱团核心玩家，快速确认队友；若查到有杀戮行为的玩家，先私下与信息位核对，再公开指控。</t>
-  </si>
-  <si>
-    <t>通灵者</t>
-  </si>
-  <si>
-    <t>随时可查看场上存活幽灵的数量。</t>
-  </si>
-  <si>
-    <t>辅助型信息位，通过幽灵数变化判断是否有隐刀，帮助团队梳理局势。</t>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>秒查看一次幽灵数，记录人数变化时间；中期若幽灵数增加但无人报警，立即提醒团队有隐刀，排查期间单独行动的玩家；后期结合幽灵数判断剩余敌人数量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>指导团队投票。</t>
+    </r>
+  </si>
+  <si>
+    <t>幽灵数变化后，同步报出时间点，方便队友对应自身动线排查；可故意隐瞒部分信息，试探其他玩家反应。</t>
+  </si>
+  <si>
+    <t>观鸟者</t>
+  </si>
+  <si>
+    <t>可穿墙观察视野，自身视野大幅缩小，关灯等设施破坏时技能失效。</t>
+  </si>
+  <si>
+    <t>隐蔽侦查型角色，适合躲在安全点位穿墙洞察墙后动静，收集敌方行踪。</t>
+  </si>
+  <si>
+    <t>开局找通风口、墙角等隐蔽点位，开启技能观察周围动线；中期重点监控任务点、走廊等关键位置，记录玩家互动；后期将观察到的可疑动线公开，配合团队锁定凶手。</t>
+  </si>
+  <si>
+    <t>开启技能时尽量背靠墙体，避免被身后玩家偷袭；不轻易暴露侦查点位，防止鸭子针对性反制。</t>
+  </si>
+  <si>
+    <t>殡仪员</t>
+  </si>
+  <si>
+    <t>靠近尸体时，可查看死者的具体身份。</t>
+  </si>
+  <si>
+    <t>快速明确阵亡者阵营，排除好人坑位，避免误判队友。</t>
+  </si>
+  <si>
+    <t>开局优先靠近任务密集区，等待尸体刷新；中期发现尸体后第一时间查看身份，会议上明确告知阵亡者阵营，排除好人坑；后期结合死者身份和动线，倒推凶手范围。</t>
+  </si>
+  <si>
+    <t>发现尸体后先观察周围玩家再查身份，避免被凶手当场击杀灭口；报身份时只说阵营，必要时再爆具体角色，防止鸭子针对性伪装。</t>
+  </si>
+  <si>
+    <t>模仿者</t>
+  </si>
+  <si>
+    <t>在鸭阵营视角中显示为红名（鸭子同类），被鸭子误认为队友。</t>
+  </si>
+  <si>
+    <t>卧底型好人，可混入鸭群骗取信息、搅乱敌方节奏，适合擅长伪装的玩家。</t>
   </si>
   <si>
     <r>
@@ -406,7 +506,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>开局每</t>
+      <t>开局故意脱离大部队，制造</t>
     </r>
     <r>
       <rPr>
@@ -415,77 +515,35 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>秒查看一次幽灵数，记录人数变化时间；中期若幽灵数增加但无人报警，立即提醒团队有隐刀，排查期间单独行动的玩家；后期结合幽灵数判断剩余敌人数量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>指导团队投票。</t>
-    </r>
-  </si>
-  <si>
-    <t>幽灵数变化后，同步报出时间点，方便队友对应自身动线排查；可故意隐瞒部分信息，试探其他玩家反应。</t>
-  </si>
-  <si>
-    <t>观鸟者</t>
-  </si>
-  <si>
-    <t>可穿墙观察视野，自身视野大幅缩小，关灯等设施破坏时技能失效。</t>
-  </si>
-  <si>
-    <t>隐蔽侦查型角色，适合躲在安全点位穿墙洞察墙后动静，收集敌方行踪。</t>
-  </si>
-  <si>
-    <t>开局找通风口、墙角等隐蔽点位，开启技能观察周围动线；中期重点监控任务点、走廊等关键位置，记录玩家互动；后期将观察到的可疑动线公开，配合团队锁定凶手。</t>
-  </si>
-  <si>
-    <t>开启技能时尽量背靠墙体，避免被身后玩家偷袭；不轻易暴露侦查点位，防止鸭子针对性反制。</t>
-  </si>
-  <si>
-    <t>殡仪员</t>
-  </si>
-  <si>
-    <t>靠近尸体时，可查看死者的具体身份。</t>
-  </si>
-  <si>
-    <t>快速明确阵亡者阵营，排除好人坑位，避免误判队友。</t>
-  </si>
-  <si>
-    <t>开局优先靠近任务密集区，等待尸体刷新；中期发现尸体后第一时间查看身份，会议上明确告知阵亡者阵营，排除好人坑；后期结合死者身份和动线，倒推凶手范围。</t>
-  </si>
-  <si>
-    <t>发现尸体后先观察周围玩家再查身份，避免被凶手当场击杀灭口；报身份时只说阵营，必要时再爆具体角色，防止鸭子针对性伪装。</t>
-  </si>
-  <si>
-    <t>模仿者</t>
-  </si>
-  <si>
-    <t>在鸭阵营视角中显示为红名（鸭子同类），被鸭子误认为队友。</t>
-  </si>
-  <si>
-    <t>卧底型好人，可混入鸭群骗取信息、搅乱敌方节奏，适合擅长伪装的玩家。</t>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>像鸭子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的动线；中期尝试接触单独行动的玩家，混入鸭群获取刀人计划；后期在会议上悄悄透露鸭群信息，引导好人投票，同时避免被鸭子识破。</t>
+    </r>
   </si>
   <si>
     <r>
@@ -496,7 +554,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>开局故意脱离大部队，制造</t>
+      <t>混入鸭群后不主动提刀人，等鸭子分配任务，再暗中传递信息；若被鸭子怀疑，可主动</t>
     </r>
     <r>
       <rPr>
@@ -514,7 +572,7 @@
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t>像鸭子</t>
+      <t>卖</t>
     </r>
     <r>
       <rPr>
@@ -532,54 +590,6 @@
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t>的动线；中期尝试接触单独行动的玩家，混入鸭群获取刀人计划；后期在会议上悄悄透露鸭群信息，引导好人投票，同时避免被鸭子识破。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>混入鸭群后不主动提刀人，等鸭子分配任务，再暗中传递信息；若被鸭子怀疑，可主动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>卖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
       <t>一个好人给鸭子，获取信任。</t>
     </r>
   </si>
@@ -605,7 +615,7 @@
     <t>目睹其他玩家被谋杀后，短时间内获得刀人能力，连续目击可刷新技能。</t>
   </si>
   <si>
-    <t>可接替警长、正义使者补刀，需紧跟大部队，及时响应谋杀事件。</t>
+    <t>可接替警长、正义使者补刀，需跟紧大部队，及时响应谋杀事件。</t>
   </si>
   <si>
     <t>开局紧跟大部队，扩大视野范围，争取目击谋杀现场；中期获得刀人能力后，立即追杀凶手，或在会议上指认后动手；后期若多次目击，可主动带队清理可疑玩家，补充阵营战力。</t>
